--- a/dataset/Test1/Inp1.xlsx
+++ b/dataset/Test1/Inp1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t xml:space="preserve">TutorID</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t xml:space="preserve">Jim Rose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bob Tulip</t>
   </si>
   <si>
     <t xml:space="preserve">Ian Petal</t>
@@ -52,6 +49,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -111,8 +109,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -243,43 +245,41 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>305</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>203</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
-        <v>102</v>
-      </c>
-      <c r="B4" s="0" t="s">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
